--- a/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,73</t>
+          <t>0,01; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,74</t>
+          <t>-1,33; 0,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,99</t>
+          <t>-3,78; 3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 1098,51</t>
+          <t>-33,18; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 778,44</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,83</t>
+          <t>-0,65; 0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,59</t>
+          <t>-1,95; 0,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,33</t>
+          <t>-0,94; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,74</t>
+          <t>-0,31; 3,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,66; 110,21</t>
+          <t>-85,79; 114,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 360,15</t>
+          <t>-78,78; 363,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 1198,85</t>
+          <t>-44,98; 1267,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,2</t>
+          <t>-1,01; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,49</t>
+          <t>0,2; 3,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,81</t>
+          <t>-0,05; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 401,17</t>
+          <t>-72,09; 471,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 572,61</t>
+          <t>-2,86; 602,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 1259,65</t>
+          <t>-34,54; 1342,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 490,73</t>
+          <t>-14,12; 448,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,99</t>
+          <t>-1,38; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,34</t>
+          <t>-1,62; 2,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,78</t>
+          <t>-0,97; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,54</t>
+          <t>-1,08; 2,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 267,21</t>
+          <t>-59,16; 233,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 210,96</t>
+          <t>-53,17; 210,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 426,18</t>
+          <t>-58,19; 368,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 203,7</t>
+          <t>-31,36; 204,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,73</t>
+          <t>-0,04; 2,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,72</t>
+          <t>-2,22; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,07</t>
+          <t>-1,11; 3,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,01</t>
+          <t>-2,22; 0,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,96; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 144,77</t>
+          <t>-66,06; 163,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 384,04</t>
+          <t>-60,31; 458,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 58,09</t>
+          <t>-59,24; 53,1</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,72</t>
+          <t>-1,65; 1,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,03</t>
+          <t>-4,75; -0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,19</t>
+          <t>-1,26; 3,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 69,15</t>
+          <t>-0,46; 65,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 407,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,54</t>
+          <t>-100,0; 43,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 424,47</t>
+          <t>-53,12; 408,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 4822,68</t>
+          <t>-13,51; 4962,55</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,44</t>
+          <t>-4,46; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,61</t>
+          <t>-4,28; 1,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,17</t>
+          <t>0,02; 4,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,61</t>
+          <t>-0,82; 3,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 98,22</t>
+          <t>-82,74; 116,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 105,29</t>
+          <t>-77,67; 107,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,51; —</t>
+          <t>-49,72; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 186,44</t>
+          <t>-21,86; 190,58</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,77</t>
+          <t>-0,26; 0,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,94</t>
+          <t>-0,47; 0,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,21</t>
+          <t>0,09; 1,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 23,22</t>
+          <t>0,4; 23,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 109,91</t>
+          <t>-23,31; 118,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 64,93</t>
+          <t>-21,19; 57,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 179,03</t>
+          <t>7,09; 167,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,85; 1267,66</t>
+          <t>18,79; 1251,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,81%</t>
+          <t>-13,39%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,74</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,67</t>
+          <t>-1,27; 0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,09</t>
+          <t>-4,04; 3,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,18; —</t>
+          <t>-36,59; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,72; 314,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>172,3%</t>
+          <t>208,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,81</t>
+          <t>-0,59; 0,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,69</t>
+          <t>-2,08; 0,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,34</t>
+          <t>-0,8; 1,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,93</t>
+          <t>-0,08; 3,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,79; 114,42</t>
+          <t>-88,51; 123,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 363,79</t>
+          <t>-74,02; 376,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 1267,06</t>
+          <t>-38,26; 1310,99</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>119,91%</t>
+          <t>134,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,37</t>
+          <t>-0,96; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,62</t>
+          <t>0,14; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,01; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,8</t>
+          <t>0,36; 3,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 471,27</t>
+          <t>-70,52; 554,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 602,29</t>
+          <t>-3,45; 578,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 1342,83</t>
+          <t>-36,14; 1709,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 448,76</t>
+          <t>3,27; 520,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,9</t>
+          <t>-1,57; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,37</t>
+          <t>-1,5; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,61</t>
+          <t>-0,99; 1,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,5</t>
+          <t>-1,69; 1,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,16; 233,98</t>
+          <t>-65,92; 178,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 210,06</t>
+          <t>-50,36; 250,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 368,48</t>
+          <t>-66,19; 272,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 204,77</t>
+          <t>-43,31; 83,38</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-15,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,89</t>
+          <t>-0,2; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,99</t>
+          <t>-2,42; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,12</t>
+          <t>-1,09; 3,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,9</t>
+          <t>-2,01; 1,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,96; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 163,35</t>
+          <t>-68,34; 130,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 458,24</t>
+          <t>-50,69; 417,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 53,1</t>
+          <t>-55,48; 65,17</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32,99</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1242,71%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,59</t>
+          <t>-1,46; 1,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,0</t>
+          <t>-4,64; 0,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,21</t>
+          <t>-1,22; 3,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 65,94</t>
+          <t>-1,12; 2,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,0; 473,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 43,95</t>
+          <t>-100,0; 37,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 408,82</t>
+          <t>-53,92; 388,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 4962,55</t>
+          <t>-31,18; 181,09</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,59</t>
+          <t>-4,47; 1,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,72</t>
+          <t>-4,21; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,12</t>
+          <t>0,03; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,68</t>
+          <t>-0,71; 3,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-82,74; 116,76</t>
+          <t>-82,8; 124,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-77,67; 107,23</t>
+          <t>-74,1; 130,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,72; —</t>
+          <t>-27,87; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 190,58</t>
+          <t>-18,97; 183,42</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>288,49%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,76</t>
+          <t>-0,26; 0,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,88</t>
+          <t>-0,46; 0,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,2</t>
+          <t>0,11; 1,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 23,21</t>
+          <t>0,03; 1,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 118,21</t>
+          <t>-26,02; 112,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 57,91</t>
+          <t>-21,21; 64,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,09; 167,0</t>
+          <t>4,71; 172,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,79; 1251,88</t>
+          <t>0,47; 80,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
